--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -3588,7 +3588,7 @@
         <v>111769051</v>
       </c>
       <c r="B28" t="n">
-        <v>74583</v>
+        <v>74585</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>111769133</v>
       </c>
       <c r="B30" t="n">
-        <v>87343</v>
+        <v>87345</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>117791978</v>
       </c>
       <c r="B113" t="n">
-        <v>90517</v>
+        <v>90519</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12858,10 +12858,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>117791457</v>
+        <v>117786458</v>
       </c>
       <c r="B114" t="n">
-        <v>97742</v>
+        <v>79563</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12870,38 +12870,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Kälmyren (Kälmyren), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478062</v>
+        <v>478409</v>
       </c>
       <c r="R114" t="n">
-        <v>7034125</v>
+        <v>7034576</v>
       </c>
       <c r="S114" t="n">
         <v>20</v>
@@ -12960,10 +12960,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>117786458</v>
+        <v>117791457</v>
       </c>
       <c r="B115" t="n">
-        <v>79561</v>
+        <v>97744</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12972,38 +12972,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Kälmyren (Kälmyren), Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>478409</v>
+        <v>478062</v>
       </c>
       <c r="R115" t="n">
-        <v>7034576</v>
+        <v>7034125</v>
       </c>
       <c r="S115" t="n">
         <v>20</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13273,6 +13273,516 @@
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>118860068</v>
+      </c>
+      <c r="B118" t="n">
+        <v>97844</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>620</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Skogsfru</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Epipogium aphyllum</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>478130</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7035017</v>
+      </c>
+      <c r="S118" t="n">
+        <v>20</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118859946</v>
+      </c>
+      <c r="B119" t="n">
+        <v>97844</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>620</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Skogsfru</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Epipogium aphyllum</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>478088</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7035105</v>
+      </c>
+      <c r="S119" t="n">
+        <v>20</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118860811</v>
+      </c>
+      <c r="B120" t="n">
+        <v>97752</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>504</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Kälmyren (Kälmyren), Jmt</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>477904</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7034287</v>
+      </c>
+      <c r="S120" t="n">
+        <v>20</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>118859685</v>
+      </c>
+      <c r="B121" t="n">
+        <v>91201</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>67</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>478092</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7035069</v>
+      </c>
+      <c r="S121" t="n">
+        <v>20</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>118860514</v>
+      </c>
+      <c r="B122" t="n">
+        <v>86296</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Schaeff. : Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>478229</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7034631</v>
+      </c>
+      <c r="S122" t="n">
+        <v>20</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -13275,10 +13275,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118860068</v>
+        <v>118860514</v>
       </c>
       <c r="B118" t="n">
-        <v>97844</v>
+        <v>86296</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13287,25 +13287,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>620</v>
+        <v>3624</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Cortinarius glaucopus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13315,10 +13315,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478130</v>
+        <v>478229</v>
       </c>
       <c r="R118" t="n">
-        <v>7035017</v>
+        <v>7034631</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -13581,10 +13581,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118859685</v>
+        <v>118860068</v>
       </c>
       <c r="B121" t="n">
-        <v>91201</v>
+        <v>97844</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13593,25 +13593,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>67</v>
+        <v>620</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13621,10 +13621,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478092</v>
+        <v>478130</v>
       </c>
       <c r="R121" t="n">
-        <v>7035069</v>
+        <v>7035017</v>
       </c>
       <c r="S121" t="n">
         <v>20</v>
@@ -13683,10 +13683,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118860514</v>
+        <v>118859685</v>
       </c>
       <c r="B122" t="n">
-        <v>86296</v>
+        <v>91201</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13695,25 +13695,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3624</v>
+        <v>67</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13723,10 +13723,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478229</v>
+        <v>478092</v>
       </c>
       <c r="R122" t="n">
-        <v>7034631</v>
+        <v>7035069</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -13275,10 +13275,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118860514</v>
+        <v>118859946</v>
       </c>
       <c r="B118" t="n">
-        <v>86296</v>
+        <v>97844</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13287,25 +13287,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3624</v>
+        <v>620</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13315,10 +13315,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478229</v>
+        <v>478088</v>
       </c>
       <c r="R118" t="n">
-        <v>7034631</v>
+        <v>7035105</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -13377,7 +13377,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118859946</v>
+        <v>118860068</v>
       </c>
       <c r="B119" t="n">
         <v>97844</v>
@@ -13417,10 +13417,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478088</v>
+        <v>478130</v>
       </c>
       <c r="R119" t="n">
-        <v>7035105</v>
+        <v>7035017</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -13479,10 +13479,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118860811</v>
+        <v>118859685</v>
       </c>
       <c r="B120" t="n">
-        <v>97752</v>
+        <v>91201</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13491,38 +13491,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>504</v>
+        <v>67</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Kälmyren (Kälmyren), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>477904</v>
+        <v>478092</v>
       </c>
       <c r="R120" t="n">
-        <v>7034287</v>
+        <v>7035069</v>
       </c>
       <c r="S120" t="n">
         <v>20</v>
@@ -13581,10 +13581,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118860068</v>
+        <v>118860514</v>
       </c>
       <c r="B121" t="n">
-        <v>97844</v>
+        <v>86296</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13593,25 +13593,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>620</v>
+        <v>3624</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Cortinarius glaucopus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13621,10 +13621,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478130</v>
+        <v>478229</v>
       </c>
       <c r="R121" t="n">
-        <v>7035017</v>
+        <v>7034631</v>
       </c>
       <c r="S121" t="n">
         <v>20</v>
@@ -13683,10 +13683,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118859685</v>
+        <v>118860811</v>
       </c>
       <c r="B122" t="n">
-        <v>91201</v>
+        <v>97752</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13695,38 +13695,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>67</v>
+        <v>504</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Kälmyren (Kälmyren), Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478092</v>
+        <v>477904</v>
       </c>
       <c r="R122" t="n">
-        <v>7035069</v>
+        <v>7034287</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -13065,7 +13065,7 @@
         <v>118413013</v>
       </c>
       <c r="B116" t="n">
-        <v>97848</v>
+        <v>97855</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>118699380</v>
       </c>
       <c r="B117" t="n">
-        <v>86138</v>
+        <v>86145</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13275,10 +13275,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118859946</v>
+        <v>118860514</v>
       </c>
       <c r="B118" t="n">
-        <v>97844</v>
+        <v>86303</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13287,25 +13287,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>620</v>
+        <v>3624</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Cortinarius glaucopus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13315,10 +13315,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478088</v>
+        <v>478229</v>
       </c>
       <c r="R118" t="n">
-        <v>7035105</v>
+        <v>7034631</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -13377,10 +13377,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118860068</v>
+        <v>118859946</v>
       </c>
       <c r="B119" t="n">
-        <v>97844</v>
+        <v>97851</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13417,10 +13417,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>478130</v>
+        <v>478088</v>
       </c>
       <c r="R119" t="n">
-        <v>7035017</v>
+        <v>7035105</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -13482,7 +13482,7 @@
         <v>118859685</v>
       </c>
       <c r="B120" t="n">
-        <v>91201</v>
+        <v>91208</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13581,10 +13581,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118860514</v>
+        <v>118860811</v>
       </c>
       <c r="B121" t="n">
-        <v>86296</v>
+        <v>97759</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13597,34 +13597,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3624</v>
+        <v>504</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Kälmyren (Kälmyren), Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478229</v>
+        <v>477904</v>
       </c>
       <c r="R121" t="n">
-        <v>7034631</v>
+        <v>7034287</v>
       </c>
       <c r="S121" t="n">
         <v>20</v>
@@ -13683,10 +13683,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118860811</v>
+        <v>118860068</v>
       </c>
       <c r="B122" t="n">
-        <v>97752</v>
+        <v>97851</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13695,38 +13695,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>504</v>
+        <v>620</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Kälmyren (Kälmyren), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>477904</v>
+        <v>478130</v>
       </c>
       <c r="R122" t="n">
-        <v>7034287</v>
+        <v>7035017</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -13275,10 +13275,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118860514</v>
+        <v>118860068</v>
       </c>
       <c r="B118" t="n">
-        <v>86303</v>
+        <v>97851</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13287,25 +13287,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3624</v>
+        <v>620</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13315,10 +13315,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>478229</v>
+        <v>478130</v>
       </c>
       <c r="R118" t="n">
-        <v>7034631</v>
+        <v>7035017</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -13479,10 +13479,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118859685</v>
+        <v>118860811</v>
       </c>
       <c r="B120" t="n">
-        <v>91208</v>
+        <v>97759</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13491,38 +13491,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>67</v>
+        <v>504</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Stenbäcken (Stenbäcken), Jmt</t>
+          <t>Kälmyren (Kälmyren), Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478092</v>
+        <v>477904</v>
       </c>
       <c r="R120" t="n">
-        <v>7035069</v>
+        <v>7034287</v>
       </c>
       <c r="S120" t="n">
         <v>20</v>
@@ -13581,10 +13581,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118860811</v>
+        <v>118859685</v>
       </c>
       <c r="B121" t="n">
-        <v>97759</v>
+        <v>91208</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13593,38 +13593,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>504</v>
+        <v>67</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Kälmyren (Kälmyren), Jmt</t>
+          <t>Stenbäcken (Stenbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>477904</v>
+        <v>478092</v>
       </c>
       <c r="R121" t="n">
-        <v>7034287</v>
+        <v>7035069</v>
       </c>
       <c r="S121" t="n">
         <v>20</v>
@@ -13683,10 +13683,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118860068</v>
+        <v>118860514</v>
       </c>
       <c r="B122" t="n">
-        <v>97851</v>
+        <v>86303</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13695,25 +13695,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>620</v>
+        <v>3624</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Cortinarius glaucopus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff. : Fr.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13723,10 +13723,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478130</v>
+        <v>478229</v>
       </c>
       <c r="R122" t="n">
-        <v>7035017</v>
+        <v>7034631</v>
       </c>
       <c r="S122" t="n">
         <v>20</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14178,7 +14178,7 @@
         <v>119930657</v>
       </c>
       <c r="B128" t="n">
-        <v>86410</v>
+        <v>86427</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -13965,7 +13965,7 @@
         <v>119223449</v>
       </c>
       <c r="B126" t="n">
-        <v>91375</v>
+        <v>91385</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>121241485</v>
       </c>
       <c r="B129" t="n">
-        <v>90745</v>
+        <v>90755</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>121241420</v>
       </c>
       <c r="B130" t="n">
-        <v>77982</v>
+        <v>77985</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>121241497</v>
       </c>
       <c r="B131" t="n">
-        <v>86234</v>
+        <v>86239</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -13965,7 +13965,7 @@
         <v>119223449</v>
       </c>
       <c r="B126" t="n">
-        <v>91385</v>
+        <v>91397</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14281,10 +14281,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121241485</v>
+        <v>121241497</v>
       </c>
       <c r="B129" t="n">
-        <v>90755</v>
+        <v>86245</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14293,25 +14293,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3277</v>
+        <v>249228</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14324,10 +14324,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478251</v>
+        <v>478054</v>
       </c>
       <c r="R129" t="n">
-        <v>7034663</v>
+        <v>7035126</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14390,7 +14390,7 @@
         <v>121241420</v>
       </c>
       <c r="B130" t="n">
-        <v>77985</v>
+        <v>77988</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14493,10 +14493,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121241497</v>
+        <v>121241485</v>
       </c>
       <c r="B131" t="n">
-        <v>86239</v>
+        <v>90767</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14505,25 +14505,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>249228</v>
+        <v>3277</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14536,10 +14536,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478054</v>
+        <v>478251</v>
       </c>
       <c r="R131" t="n">
-        <v>7035126</v>
+        <v>7034663</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -13965,7 +13965,7 @@
         <v>119223449</v>
       </c>
       <c r="B126" t="n">
-        <v>91397</v>
+        <v>91398</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14387,10 +14387,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121241420</v>
+        <v>121241485</v>
       </c>
       <c r="B130" t="n">
-        <v>77988</v>
+        <v>90768</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14403,21 +14403,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6437</v>
+        <v>3277</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14430,10 +14430,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>477701</v>
+        <v>478251</v>
       </c>
       <c r="R130" t="n">
-        <v>7034372</v>
+        <v>7034663</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14493,10 +14493,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121241485</v>
+        <v>121241420</v>
       </c>
       <c r="B131" t="n">
-        <v>90767</v>
+        <v>77988</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14509,21 +14509,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3277</v>
+        <v>6437</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14536,10 +14536,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478251</v>
+        <v>477701</v>
       </c>
       <c r="R131" t="n">
-        <v>7034663</v>
+        <v>7034372</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -13965,7 +13965,7 @@
         <v>119223449</v>
       </c>
       <c r="B126" t="n">
-        <v>91398</v>
+        <v>91401</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14281,10 +14281,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121241497</v>
+        <v>121241420</v>
       </c>
       <c r="B129" t="n">
-        <v>86245</v>
+        <v>77991</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14293,25 +14293,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>249228</v>
+        <v>6437</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14324,10 +14324,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478054</v>
+        <v>477701</v>
       </c>
       <c r="R129" t="n">
-        <v>7035126</v>
+        <v>7034372</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14390,7 +14390,7 @@
         <v>121241485</v>
       </c>
       <c r="B130" t="n">
-        <v>90768</v>
+        <v>90771</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14493,10 +14493,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121241420</v>
+        <v>121241497</v>
       </c>
       <c r="B131" t="n">
-        <v>77988</v>
+        <v>86248</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14505,25 +14505,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6437</v>
+        <v>249228</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14536,10 +14536,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>477701</v>
+        <v>478054</v>
       </c>
       <c r="R131" t="n">
-        <v>7034372</v>
+        <v>7035126</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14281,10 +14281,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121241420</v>
+        <v>121241497</v>
       </c>
       <c r="B129" t="n">
-        <v>77991</v>
+        <v>86248</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14293,25 +14293,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6437</v>
+        <v>249228</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14324,10 +14324,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>477701</v>
+        <v>478054</v>
       </c>
       <c r="R129" t="n">
-        <v>7034372</v>
+        <v>7035126</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14387,10 +14387,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121241485</v>
+        <v>121241420</v>
       </c>
       <c r="B130" t="n">
-        <v>90771</v>
+        <v>77991</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14403,21 +14403,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3277</v>
+        <v>6437</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14430,10 +14430,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478251</v>
+        <v>477701</v>
       </c>
       <c r="R130" t="n">
-        <v>7034663</v>
+        <v>7034372</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14493,10 +14493,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121241497</v>
+        <v>121241485</v>
       </c>
       <c r="B131" t="n">
-        <v>86248</v>
+        <v>90771</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14505,25 +14505,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>249228</v>
+        <v>3277</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14536,10 +14536,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478054</v>
+        <v>478251</v>
       </c>
       <c r="R131" t="n">
-        <v>7035126</v>
+        <v>7034663</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14284,7 +14284,7 @@
         <v>121241497</v>
       </c>
       <c r="B129" t="n">
-        <v>86248</v>
+        <v>86252</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>121241420</v>
       </c>
       <c r="B130" t="n">
-        <v>77991</v>
+        <v>77992</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>121241485</v>
       </c>
       <c r="B131" t="n">
-        <v>90771</v>
+        <v>90777</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14284,7 +14284,7 @@
         <v>121241497</v>
       </c>
       <c r="B129" t="n">
-        <v>86252</v>
+        <v>86253</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14387,10 +14387,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121241420</v>
+        <v>121241485</v>
       </c>
       <c r="B130" t="n">
-        <v>77992</v>
+        <v>90778</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14403,21 +14403,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6437</v>
+        <v>3277</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14430,10 +14430,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>477701</v>
+        <v>478251</v>
       </c>
       <c r="R130" t="n">
-        <v>7034372</v>
+        <v>7034663</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14493,10 +14493,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121241485</v>
+        <v>121241420</v>
       </c>
       <c r="B131" t="n">
-        <v>90777</v>
+        <v>77993</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14509,21 +14509,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3277</v>
+        <v>6437</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14536,10 +14536,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478251</v>
+        <v>477701</v>
       </c>
       <c r="R131" t="n">
-        <v>7034663</v>
+        <v>7034372</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14281,10 +14281,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121241497</v>
+        <v>121241485</v>
       </c>
       <c r="B129" t="n">
-        <v>86253</v>
+        <v>90778</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14293,25 +14293,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>249228</v>
+        <v>3277</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14324,10 +14324,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478054</v>
+        <v>478251</v>
       </c>
       <c r="R129" t="n">
-        <v>7035126</v>
+        <v>7034663</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14387,10 +14387,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121241485</v>
+        <v>121241420</v>
       </c>
       <c r="B130" t="n">
-        <v>90778</v>
+        <v>77993</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14403,21 +14403,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3277</v>
+        <v>6437</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14430,10 +14430,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478251</v>
+        <v>477701</v>
       </c>
       <c r="R130" t="n">
-        <v>7034663</v>
+        <v>7034372</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14493,10 +14493,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121241420</v>
+        <v>121241497</v>
       </c>
       <c r="B131" t="n">
-        <v>77993</v>
+        <v>86253</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14505,25 +14505,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6437</v>
+        <v>249228</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14536,10 +14536,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>477701</v>
+        <v>478054</v>
       </c>
       <c r="R131" t="n">
-        <v>7034372</v>
+        <v>7035126</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14281,10 +14281,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121241485</v>
+        <v>121241420</v>
       </c>
       <c r="B129" t="n">
-        <v>90778</v>
+        <v>77993</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14297,21 +14297,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3277</v>
+        <v>6437</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14324,10 +14324,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478251</v>
+        <v>477701</v>
       </c>
       <c r="R129" t="n">
-        <v>7034663</v>
+        <v>7034372</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14387,10 +14387,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121241420</v>
+        <v>121241485</v>
       </c>
       <c r="B130" t="n">
-        <v>77993</v>
+        <v>90778</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14403,21 +14403,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6437</v>
+        <v>3277</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14430,10 +14430,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>477701</v>
+        <v>478251</v>
       </c>
       <c r="R130" t="n">
-        <v>7034372</v>
+        <v>7034663</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -13042,7 +13042,7 @@
         <v>118699380</v>
       </c>
       <c r="B117" t="n">
-        <v>86097</v>
+        <v>86098</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -13042,7 +13042,7 @@
         <v>118699380</v>
       </c>
       <c r="B117" t="n">
-        <v>86098</v>
+        <v>86103</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -13042,7 +13042,7 @@
         <v>118699380</v>
       </c>
       <c r="B117" t="n">
-        <v>86103</v>
+        <v>86107</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY131"/>
+  <dimension ref="A1:AY137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14597,6 +14597,679 @@
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>125658526</v>
+      </c>
+      <c r="B132" t="n">
+        <v>88512</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>510</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>477053</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7033618</v>
+      </c>
+      <c r="S132" t="n">
+        <v>15</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>Stamnät grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>125660017</v>
+      </c>
+      <c r="B133" t="n">
+        <v>91865</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>67</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Stenbäcken, Rensbodarna, Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>477214</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7033393</v>
+      </c>
+      <c r="S133" t="n">
+        <v>15</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>Stamnät grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>125657137</v>
+      </c>
+      <c r="B134" t="n">
+        <v>79536</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Kälmyren, Stenbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>477681</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7034173</v>
+      </c>
+      <c r="S134" t="n">
+        <v>15</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>125656747</v>
+      </c>
+      <c r="B135" t="n">
+        <v>79026</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>864</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Stenbäcken, Rensbodarna, Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>477786</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7034244</v>
+      </c>
+      <c r="S135" t="n">
+        <v>15</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>Glest trädbevuxet rikkärr med gran och tall</t>
+        </is>
+      </c>
+      <c r="AL135" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>125657132</v>
+      </c>
+      <c r="B136" t="n">
+        <v>77874</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Kälmyren, Stenbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>477681</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7034173</v>
+      </c>
+      <c r="S136" t="n">
+        <v>15</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>125655659</v>
+      </c>
+      <c r="B137" t="n">
+        <v>75020</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>310</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Nordlig nållav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Chaenotheca laevigata</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>478144</v>
+      </c>
+      <c r="R137" t="n">
+        <v>7035007</v>
+      </c>
+      <c r="S137" t="n">
+        <v>15</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14599,15 +14599,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125658526</v>
+        <v>125656747</v>
       </c>
       <c r="B132" t="n">
-        <v>88512</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79046</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14615,21 +14610,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>510</v>
+        <v>864</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14638,14 +14633,14 @@
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Stenbäcken, Stenbäcken, Jmt</t>
+          <t>Stenbäcken, Rensbodarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>477053</v>
+        <v>477786</v>
       </c>
       <c r="R132" t="n">
-        <v>7033618</v>
+        <v>7034244</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14692,7 +14687,17 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>Stamnät grannaturskog</t>
+          <t>Glest trädbevuxet rikkärr med gran och tall</t>
+        </is>
+      </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -14710,53 +14715,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125660017</v>
+        <v>125657137</v>
       </c>
       <c r="B133" t="n">
-        <v>91865</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79556</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>67</v>
+        <v>229821</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Stenbäcken, Rensbodarna, Aspås, Jmt</t>
+          <t>Kälmyren, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>477214</v>
+        <v>477681</v>
       </c>
       <c r="R133" t="n">
-        <v>7033393</v>
+        <v>7034173</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14797,14 +14794,8 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>Stamnät grannaturskog</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
@@ -14821,50 +14812,48 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125657137</v>
+        <v>125660017</v>
       </c>
       <c r="B134" t="n">
-        <v>79536</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91919</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>229821</v>
+        <v>67</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kälmyren, Stenbäcken, Jmt</t>
+          <t>Stenbäcken, Rensbodarna, Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>477681</v>
+        <v>477214</v>
       </c>
       <c r="R134" t="n">
-        <v>7034173</v>
+        <v>7033393</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14905,8 +14894,14 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>Stamnät grannaturskog</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
@@ -14923,15 +14918,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125656747</v>
+        <v>125657132</v>
       </c>
       <c r="B135" t="n">
-        <v>79026</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77916</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14939,37 +14929,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>864</v>
+        <v>6487</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Stenbäcken, Rensbodarna, Aspås, Jmt</t>
+          <t>Kälmyren, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>477786</v>
+        <v>477681</v>
       </c>
       <c r="R135" t="n">
-        <v>7034244</v>
+        <v>7034173</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15010,24 +14997,8 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>Glest trädbevuxet rikkärr med gran och tall</t>
-        </is>
-      </c>
-      <c r="AL135" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
@@ -15044,15 +15015,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125657132</v>
+        <v>125655659</v>
       </c>
       <c r="B136" t="n">
-        <v>77874</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75061</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15060,34 +15026,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6487</v>
+        <v>310</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Kälmyren, Stenbäcken, Jmt</t>
+          <t>Stenbäcken, Stenbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>477681</v>
+        <v>478144</v>
       </c>
       <c r="R136" t="n">
-        <v>7034173</v>
+        <v>7035007</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15128,8 +15097,29 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
@@ -15146,15 +15136,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125655659</v>
+        <v>125658526</v>
       </c>
       <c r="B137" t="n">
-        <v>75020</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88626</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15162,21 +15147,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>310</v>
+        <v>510</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15189,10 +15174,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>478144</v>
+        <v>477053</v>
       </c>
       <c r="R137" t="n">
-        <v>7035007</v>
+        <v>7033618</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15239,22 +15224,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
+          <t>Stamnät grannaturskog</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14815,7 +14815,7 @@
         <v>125660017</v>
       </c>
       <c r="B134" t="n">
-        <v>91919</v>
+        <v>91926</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>125658526</v>
       </c>
       <c r="B137" t="n">
-        <v>88626</v>
+        <v>88633</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14602,7 +14602,7 @@
         <v>125656747</v>
       </c>
       <c r="B132" t="n">
-        <v>79046</v>
+        <v>79047</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>125657137</v>
       </c>
       <c r="B133" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>125660017</v>
       </c>
       <c r="B134" t="n">
-        <v>91926</v>
+        <v>91930</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>125657132</v>
       </c>
       <c r="B135" t="n">
-        <v>77916</v>
+        <v>77917</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>125655659</v>
       </c>
       <c r="B136" t="n">
-        <v>75061</v>
+        <v>75062</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>125658526</v>
       </c>
       <c r="B137" t="n">
-        <v>88633</v>
+        <v>88637</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14602,7 +14602,7 @@
         <v>125656747</v>
       </c>
       <c r="B132" t="n">
-        <v>79047</v>
+        <v>79051</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>125657137</v>
       </c>
       <c r="B133" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>125660017</v>
       </c>
       <c r="B134" t="n">
-        <v>91930</v>
+        <v>91934</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>125657132</v>
       </c>
       <c r="B135" t="n">
-        <v>77917</v>
+        <v>77921</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>125658526</v>
       </c>
       <c r="B137" t="n">
-        <v>88637</v>
+        <v>88641</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14602,7 +14602,7 @@
         <v>125656747</v>
       </c>
       <c r="B132" t="n">
-        <v>79051</v>
+        <v>79052</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>125657137</v>
       </c>
       <c r="B133" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>125660017</v>
       </c>
       <c r="B134" t="n">
-        <v>91934</v>
+        <v>91936</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>125657132</v>
       </c>
       <c r="B135" t="n">
-        <v>77921</v>
+        <v>77922</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>125655659</v>
       </c>
       <c r="B136" t="n">
-        <v>75062</v>
+        <v>75063</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>125658526</v>
       </c>
       <c r="B137" t="n">
-        <v>88641</v>
+        <v>88643</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14815,7 +14815,7 @@
         <v>125660017</v>
       </c>
       <c r="B134" t="n">
-        <v>91936</v>
+        <v>91938</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>125658526</v>
       </c>
       <c r="B137" t="n">
-        <v>88643</v>
+        <v>88645</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14815,7 +14815,7 @@
         <v>125660017</v>
       </c>
       <c r="B134" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>125658526</v>
       </c>
       <c r="B137" t="n">
-        <v>88645</v>
+        <v>88647</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -14602,7 +14602,7 @@
         <v>125656747</v>
       </c>
       <c r="B132" t="n">
-        <v>79052</v>
+        <v>79056</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>125657137</v>
       </c>
       <c r="B133" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>125660017</v>
       </c>
       <c r="B134" t="n">
-        <v>91940</v>
+        <v>91944</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>125657132</v>
       </c>
       <c r="B135" t="n">
-        <v>77922</v>
+        <v>77926</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>125655659</v>
       </c>
       <c r="B136" t="n">
-        <v>75063</v>
+        <v>75067</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>125658526</v>
       </c>
       <c r="B137" t="n">
-        <v>88647</v>
+        <v>88651</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15245,7 +15245,7 @@
         <v>127124336</v>
       </c>
       <c r="B138" t="n">
-        <v>77944</v>
+        <v>78004</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B139" t="n">
-        <v>91603</v>
+        <v>98434</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R139" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B140" t="n">
-        <v>98359</v>
+        <v>91677</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R140" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15245,7 +15245,7 @@
         <v>127124336</v>
       </c>
       <c r="B138" t="n">
-        <v>78004</v>
+        <v>78007</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>127124895</v>
       </c>
       <c r="B139" t="n">
-        <v>98434</v>
+        <v>98440</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>127124469</v>
       </c>
       <c r="B140" t="n">
-        <v>91677</v>
+        <v>91683</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B139" t="n">
-        <v>98440</v>
+        <v>91684</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R139" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B140" t="n">
-        <v>91683</v>
+        <v>98441</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R140" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B139" t="n">
-        <v>91684</v>
+        <v>98441</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R139" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B140" t="n">
-        <v>98441</v>
+        <v>91684</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R140" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15245,7 +15245,7 @@
         <v>127124336</v>
       </c>
       <c r="B138" t="n">
-        <v>78007</v>
+        <v>78011</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B139" t="n">
-        <v>98441</v>
+        <v>91688</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R139" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B140" t="n">
-        <v>91684</v>
+        <v>98445</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R140" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B139" t="n">
-        <v>91688</v>
+        <v>98445</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R139" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B140" t="n">
-        <v>98445</v>
+        <v>91688</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R140" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B139" t="n">
-        <v>98445</v>
+        <v>91688</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R139" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B140" t="n">
-        <v>91688</v>
+        <v>98445</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R140" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B139" t="n">
-        <v>91688</v>
+        <v>98446</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R139" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B140" t="n">
-        <v>98445</v>
+        <v>91688</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R140" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15245,7 +15245,7 @@
         <v>127124336</v>
       </c>
       <c r="B138" t="n">
-        <v>78011</v>
+        <v>78013</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B139" t="n">
-        <v>98446</v>
+        <v>91690</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R139" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B140" t="n">
-        <v>91688</v>
+        <v>98448</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R140" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B139" t="n">
-        <v>91690</v>
+        <v>98448</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R139" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B140" t="n">
-        <v>98448</v>
+        <v>91690</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R140" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B139" t="n">
-        <v>98448</v>
+        <v>91690</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R139" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B140" t="n">
-        <v>91690</v>
+        <v>98448</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R140" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B139" t="n">
-        <v>91690</v>
+        <v>98454</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R139" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B140" t="n">
-        <v>98448</v>
+        <v>91696</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R140" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15245,7 +15245,7 @@
         <v>127124336</v>
       </c>
       <c r="B138" t="n">
-        <v>78013</v>
+        <v>78016</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B139" t="n">
-        <v>98454</v>
+        <v>91699</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R139" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B140" t="n">
-        <v>91696</v>
+        <v>98457</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R140" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15245,7 +15245,7 @@
         <v>127124336</v>
       </c>
       <c r="B138" t="n">
-        <v>78016</v>
+        <v>78022</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>127124469</v>
       </c>
       <c r="B139" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>127124895</v>
       </c>
       <c r="B140" t="n">
-        <v>98457</v>
+        <v>98465</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -15245,7 +15245,7 @@
         <v>127124336</v>
       </c>
       <c r="B138" t="n">
-        <v>78022</v>
+        <v>78004</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B139" t="n">
-        <v>91707</v>
+        <v>98434</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R139" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B140" t="n">
-        <v>98465</v>
+        <v>91677</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R140" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -4185,7 +4185,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
@@ -6333,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="AE54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -10103,7 +10103,7 @@
         <v>0</v>
       </c>
       <c r="AE89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
@@ -10752,7 +10752,7 @@
         <v>0</v>
       </c>
       <c r="AE95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
@@ -15245,7 +15245,7 @@
         <v>127124336</v>
       </c>
       <c r="B138" t="n">
-        <v>78004</v>
+        <v>78022</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15344,32 +15344,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127124895</v>
+        <v>127124469</v>
       </c>
       <c r="B139" t="n">
-        <v>98434</v>
+        <v>91707</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>620</v>
+        <v>2062</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15379,10 +15379,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478255</v>
+        <v>478302</v>
       </c>
       <c r="R139" t="n">
-        <v>7034458</v>
+        <v>7034362</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15446,32 +15446,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127124469</v>
+        <v>127124895</v>
       </c>
       <c r="B140" t="n">
-        <v>91677</v>
+        <v>98465</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2062</v>
+        <v>620</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478302</v>
+        <v>478255</v>
       </c>
       <c r="R140" t="n">
-        <v>7034362</v>
+        <v>7034458</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>

--- a/artfynd/A 37096-2023 artfynd.xlsx
+++ b/artfynd/A 37096-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY145"/>
+  <dimension ref="A1:AZ145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901589</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118859685</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119223449</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125660017</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125655659</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127124336</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111769051</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117093097</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6768183</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117786555</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117791457</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118860811</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2010,6 +2075,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/155521</t>
         </is>
       </c>
     </row>
@@ -2118,6 +2188,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125658526</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269191</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2316,6 +2396,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118859946</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2413,6 +2498,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118860068</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2510,6 +2600,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119049999</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2612,6 +2707,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127124895</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2709,6 +2809,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117078381</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2810,6 +2915,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111769133</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2926,6 +3036,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125656747</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3027,6 +3142,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113419329</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3133,6 +3253,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316817</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3230,6 +3355,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901520</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3328,6 +3458,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111758748</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3425,6 +3560,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119331638</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3527,6 +3667,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127124469</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3624,6 +3769,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901625</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3728,6 +3878,11 @@
       <c r="AY31" t="inlineStr">
         <is>
           <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/751524</t>
         </is>
       </c>
     </row>
@@ -3832,6 +3987,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183906</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3931,6 +4091,11 @@
       <c r="AY33" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269189</t>
         </is>
       </c>
     </row>
@@ -4034,6 +4199,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241485</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4132,6 +4302,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111759358</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4230,6 +4405,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901611</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4327,6 +4507,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901521</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4424,6 +4609,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901522</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4521,6 +4711,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901523</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4622,6 +4817,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113006323</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4715,6 +4915,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118860514</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4816,6 +5021,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269205</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4914,6 +5124,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111758961</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5015,6 +5230,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111769034</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5116,6 +5336,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269206</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5213,6 +5438,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901588</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5314,6 +5544,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113006312</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5412,6 +5647,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111759273</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5513,6 +5753,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111769028</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5614,6 +5859,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111769093</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5715,6 +5965,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111769105</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5816,6 +6071,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111769149</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5913,6 +6173,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119223506</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6011,6 +6276,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901598</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6108,6 +6378,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901609</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6205,6 +6480,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901610</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6306,6 +6586,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241420</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6412,6 +6697,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1858451</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6518,6 +6808,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269165</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6615,6 +6910,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901593</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6712,6 +7012,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901594</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6809,6 +7114,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901595</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6906,6 +7216,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901596</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7008,6 +7323,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117078744</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7105,6 +7425,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117786458</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7202,6 +7527,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657132</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7308,6 +7638,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901590</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7414,6 +7749,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901591</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7520,6 +7860,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901592</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7626,6 +7971,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901524</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7732,6 +8082,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901526</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7838,6 +8193,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901527</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7944,6 +8304,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901528</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8050,6 +8415,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901529</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8156,6 +8526,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901530</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8262,6 +8637,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901531</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8368,6 +8748,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901532</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8474,6 +8859,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901533</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8580,6 +8970,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901534</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8686,6 +9081,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901535</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8792,6 +9192,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901536</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8898,6 +9303,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901537</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9004,6 +9414,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901538</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9110,6 +9525,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901539</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9216,6 +9636,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901540</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9322,6 +9747,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901541</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9428,6 +9858,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901542</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9534,6 +9969,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901543</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9640,6 +10080,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901552</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9746,6 +10191,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901553</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9852,6 +10302,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901554</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9958,6 +10413,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901555</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10064,6 +10524,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901556</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10169,6 +10634,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901557</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10275,6 +10745,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901559</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10381,6 +10856,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901561</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10487,6 +10967,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901563</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10593,6 +11078,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901564</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10699,6 +11189,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901565</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10816,6 +11311,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901567</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10922,6 +11422,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901568</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11028,6 +11533,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901569</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11134,6 +11644,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901570</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11240,6 +11755,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901571</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11346,6 +11866,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901572</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11452,6 +11977,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901573</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11558,6 +12088,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901574</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11664,6 +12199,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901575</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11770,6 +12310,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901576</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11876,6 +12421,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901577</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11982,6 +12532,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901578</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12088,6 +12643,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901579</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12194,6 +12754,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901580</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12300,6 +12865,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901581</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12406,6 +12976,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901582</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12512,6 +13087,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901583</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12618,6 +13198,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113006316</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12725,6 +13310,11 @@
       <c r="AY118" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113006319</t>
         </is>
       </c>
     </row>
@@ -12832,6 +13422,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901586</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12934,6 +13529,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2279399</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13031,6 +13631,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117787276</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13133,6 +13738,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111769042</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13234,6 +13844,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269163</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13331,6 +13946,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118413013</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13432,6 +14052,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269202</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13529,6 +14154,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117787268</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13630,6 +14260,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269164</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13731,6 +14366,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269185</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13832,6 +14472,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269187</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13931,6 +14576,11 @@
       <c r="AY130" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269192</t>
         </is>
       </c>
     </row>
@@ -14035,6 +14685,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121122098</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14141,6 +14796,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5679642</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14242,6 +14902,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269234</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14339,6 +15004,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901612</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14440,6 +15110,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111269176</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14537,6 +15212,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657137</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14638,6 +15318,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119930657</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14739,6 +15424,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241497</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14836,6 +15526,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901620</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14933,6 +15628,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901622</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15030,6 +15730,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111901623</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15136,6 +15841,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118699380</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15242,6 +15952,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111769169</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15348,6 +16063,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119223791</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15441,8 +16161,159 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119223258</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>